--- a/public/Factory_OS_Reference_Upload_Template.xlsx
+++ b/public/Factory_OS_Reference_Upload_Template.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rbdc7131dba7843e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" r:id="R27479aa8eb3a4810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packing" sheetId="3" r:id="R1dd442eb1a374a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="4" r:id="R1e248c2303a74e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Only" sheetId="5" r:id="R07ad5815a0f24443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Already loaded" sheetId="6" r:id="R582300d62bf046c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R5e5dc804d03a4960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" r:id="Re909736c44ab4981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packing" sheetId="3" r:id="R163e70f678084272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="4" r:id="Re1700133f7b24040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Only" sheetId="5" r:id="R02057449bc6147ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Already loaded" sheetId="6" r:id="R7a76d486e3dd4bbc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,9 +51,6 @@
     <x:t xml:space="preserve">2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Repeat Article Code, Sole Type and Size Range on EVERY row. Never leave a cell blank to mean “same as above” — each row is read on its own.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">3</x:t>
   </x:si>
   <x:si>
@@ -132,9 +129,6 @@
     <x:t xml:space="preserve">BOM — what one pair consumes</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">One row per material, per size range, per stage. Start on row 5; this import tab is intentionally blank.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Article Code</x:t>
   </x:si>
   <x:si>
@@ -153,9 +147,6 @@
     <x:t xml:space="preserve">Packing — pairs per carton</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Use one row for every BOM size range and, if required, one row for each individual size. Whole numbers only.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Pairs per Carton</x:t>
   </x:si>
   <x:si>
@@ -169,9 +160,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EXAMPLE ONLY — not imported by Factory OS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Copy this pattern into BOM, Packing and Catalogue. Do not use this sheet as an upload tab.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EXAMPLE ARTICLE</x:t>
@@ -377,7 +365,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -397,6 +385,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF8FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F2233"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F2233"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -425,7 +423,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -493,6 +491,42 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -754,12 +788,12 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="16" customHeight="1">
+    <x:row r="8" ht="30" customHeight="1">
       <x:c r="B8" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>One row per article and size range: description, MRP, machine and optional Packing Source.</x:v>
+      <x:c r="C8" s="33" t="str">
+        <x:v>One row per article and size range or individual size. MRP is optional. Write Small 7 as 7S; write Large 7 as 7 (7L is also accepted).</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="16" customHeight="1">
@@ -776,50 +810,50 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="16" customHeight="1">
+    <x:row r="12" ht="36" customHeight="1">
       <x:c r="B12" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="s">
-        <x:v>12</x:v>
+      <x:c r="C12" s="33" t="str">
+        <x:v>Repeat Article Code, Sole Type and Size Range on EVERY BOM row. In Packing/Catalogue, use a range such as 7X10 or an individual size such as 7S (Small) or 7 / 7L (Large).</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="16" customHeight="1">
       <x:c r="B13" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="16" customHeight="1">
       <x:c r="B15" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="3"/>
     </x:row>
     <x:row r="16" ht="16" customHeight="1">
       <x:c r="B16" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="16" customHeight="1">
       <x:c r="B17" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="16" customHeight="1">
       <x:c r="B18" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -832,70 +866,100 @@
     </x:row>
     <x:row r="20" ht="16" customHeight="1">
       <x:c r="B20" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="3"/>
     </x:row>
     <x:row r="21" ht="16" customHeight="1">
       <x:c r="B21" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="16" customHeight="1">
       <x:c r="B22" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C22" s="5" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="16" customHeight="1">
       <x:c r="B23" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="16" customHeight="1">
       <x:c r="B24" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="16" customHeight="1">
       <x:c r="B25" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="16" customHeight="1">
       <x:c r="B27" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="3"/>
     </x:row>
     <x:row r="28" ht="16" customHeight="1">
       <x:c r="B28" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="C28" s="5" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="16" customHeight="1">
       <x:c r="B29" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C29" s="5" t="s">
-        <x:v>37</x:v>
+    </x:row>
+    <x:row r="32" ht="30" customHeight="1">
+      <x:c r="B32" s="42" t="str">
+        <x:v>HOW S / L SIZES ARE READ</x:v>
+      </x:c>
+      <x:c r="C32" s="42"/>
+    </x:row>
+    <x:row r="33" ht="30" customHeight="1">
+      <x:c r="B33" s="43" t="str">
+        <x:v>Preferred</x:v>
+      </x:c>
+      <x:c r="C33" s="33" t="str">
+        <x:v>Write S or Small for the Small run and L or Large for the Large run. Accepted examples: 7S, S7, 7L, L7.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="30" customHeight="1">
+      <x:c r="B34" s="43" t="str">
+        <x:v>If omitted</x:v>
+      </x:c>
+      <x:c r="C34" s="33" t="str">
+        <x:v>Keep the factory order: all Small sizes first, then all Large sizes. Factory OS shows a warning whenever it uses this fallback.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="30" customHeight="1">
+      <x:c r="B35" s="43" t="str">
+        <x:v>Example</x:v>
+      </x:c>
+      <x:c r="C35" s="33" t="str">
+        <x:v>7, 8, 1, 2, 3 is read as Small 7, Small 8, then Large 1, 2, 3. After the Large run starts, later 7–13 are Large.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -907,6 +971,7 @@
     <x:mergeCell ref="B15:C15"/>
     <x:mergeCell ref="B20:C20"/>
     <x:mergeCell ref="B27:C27"/>
+    <x:mergeCell ref="B32:C32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -924,11 +989,12 @@
     <x:col min="4" max="4" width="16" customWidth="1"/>
     <x:col min="5" max="5" width="28" customWidth="1"/>
     <x:col min="7" max="7" width="15" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -938,8 +1004,8 @@
       <x:c r="G1" s="6"/>
     </x:row>
     <x:row r="2" ht="16" customHeight="1">
-      <x:c r="A2" s="7" t="s">
-        <x:v>39</x:v>
+      <x:c r="A2" s="7" t="str">
+        <x:v>Preferred: write Small or Large when a range repeats. If blank, Factory OS follows the uploaded range order: all Small ranges first, then Large.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -950,25 +1016,28 @@
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="F4" s="8" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="G4" s="8" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="s">
-        <x:v>44</x:v>
+      <x:c r="H4" s="45" t="str">
+        <x:v>Size Run (optional)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -979,6 +1048,7 @@
       <x:c r="E5" s="9"/>
       <x:c r="F5" s="10"/>
       <x:c r="G5" s="11"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="9"/>
@@ -988,6 +1058,7 @@
       <x:c r="E6" s="9"/>
       <x:c r="F6" s="10"/>
       <x:c r="G6" s="11"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="9"/>
@@ -997,6 +1068,7 @@
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="10"/>
       <x:c r="G7" s="11"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="9"/>
@@ -1006,6 +1078,7 @@
       <x:c r="E8" s="9"/>
       <x:c r="F8" s="10"/>
       <x:c r="G8" s="11"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="9"/>
@@ -1015,6 +1088,7 @@
       <x:c r="E9" s="9"/>
       <x:c r="F9" s="10"/>
       <x:c r="G9" s="11"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="9"/>
@@ -1024,6 +1098,7 @@
       <x:c r="E10" s="9"/>
       <x:c r="F10" s="10"/>
       <x:c r="G10" s="11"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="9"/>
@@ -1033,6 +1108,7 @@
       <x:c r="E11" s="9"/>
       <x:c r="F11" s="10"/>
       <x:c r="G11" s="11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9"/>
@@ -1042,6 +1118,7 @@
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="10"/>
       <x:c r="G12" s="11"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9"/>
@@ -1051,6 +1128,7 @@
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="10"/>
       <x:c r="G13" s="11"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9"/>
@@ -1060,6 +1138,7 @@
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="10"/>
       <x:c r="G14" s="11"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9"/>
@@ -1069,6 +1148,7 @@
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="10"/>
       <x:c r="G15" s="11"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9"/>
@@ -1078,6 +1158,7 @@
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="10"/>
       <x:c r="G16" s="11"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9"/>
@@ -1087,6 +1168,7 @@
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="10"/>
       <x:c r="G17" s="11"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="9"/>
@@ -1096,6 +1178,7 @@
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="10"/>
       <x:c r="G18" s="11"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9"/>
@@ -1105,6 +1188,7 @@
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="10"/>
       <x:c r="G19" s="11"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9"/>
@@ -1114,6 +1198,7 @@
       <x:c r="E20" s="9"/>
       <x:c r="F20" s="10"/>
       <x:c r="G20" s="11"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9"/>
@@ -1123,6 +1208,7 @@
       <x:c r="E21" s="9"/>
       <x:c r="F21" s="10"/>
       <x:c r="G21" s="11"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9"/>
@@ -1132,6 +1218,7 @@
       <x:c r="E22" s="9"/>
       <x:c r="F22" s="10"/>
       <x:c r="G22" s="11"/>
+      <x:c r="H22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="9"/>
@@ -1141,6 +1228,7 @@
       <x:c r="E23" s="9"/>
       <x:c r="F23" s="10"/>
       <x:c r="G23" s="11"/>
+      <x:c r="H23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="9"/>
@@ -1150,6 +1238,7 @@
       <x:c r="E24" s="9"/>
       <x:c r="F24" s="10"/>
       <x:c r="G24" s="11"/>
+      <x:c r="H24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="9"/>
@@ -1159,6 +1248,7 @@
       <x:c r="E25" s="9"/>
       <x:c r="F25" s="10"/>
       <x:c r="G25" s="11"/>
+      <x:c r="H25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="9"/>
@@ -1168,6 +1258,7 @@
       <x:c r="E26" s="9"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="11"/>
+      <x:c r="H26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9"/>
@@ -1177,6 +1268,7 @@
       <x:c r="E27" s="9"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="11"/>
+      <x:c r="H27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="9"/>
@@ -1186,6 +1278,7 @@
       <x:c r="E28" s="9"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="11"/>
+      <x:c r="H28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="9"/>
@@ -1195,6 +1288,7 @@
       <x:c r="E29" s="9"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="11"/>
+      <x:c r="H29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="9"/>
@@ -1204,6 +1298,7 @@
       <x:c r="E30" s="9"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="11"/>
+      <x:c r="H30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="9"/>
@@ -1213,6 +1308,7 @@
       <x:c r="E31" s="9"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="11"/>
+      <x:c r="H31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="9"/>
@@ -1222,6 +1318,7 @@
       <x:c r="E32" s="9"/>
       <x:c r="F32" s="10"/>
       <x:c r="G32" s="11"/>
+      <x:c r="H32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9"/>
@@ -1231,6 +1328,7 @@
       <x:c r="E33" s="9"/>
       <x:c r="F33" s="10"/>
       <x:c r="G33" s="11"/>
+      <x:c r="H33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="9"/>
@@ -1240,6 +1338,7 @@
       <x:c r="E34" s="9"/>
       <x:c r="F34" s="10"/>
       <x:c r="G34" s="11"/>
+      <x:c r="H34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9"/>
@@ -1249,6 +1348,7 @@
       <x:c r="E35" s="9"/>
       <x:c r="F35" s="10"/>
       <x:c r="G35" s="11"/>
+      <x:c r="H35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="9"/>
@@ -1258,6 +1358,7 @@
       <x:c r="E36" s="9"/>
       <x:c r="F36" s="10"/>
       <x:c r="G36" s="11"/>
+      <x:c r="H36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="9"/>
@@ -1267,6 +1368,7 @@
       <x:c r="E37" s="9"/>
       <x:c r="F37" s="10"/>
       <x:c r="G37" s="11"/>
+      <x:c r="H37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="9"/>
@@ -1276,6 +1378,7 @@
       <x:c r="E38" s="9"/>
       <x:c r="F38" s="10"/>
       <x:c r="G38" s="11"/>
+      <x:c r="H38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="9"/>
@@ -1285,6 +1388,7 @@
       <x:c r="E39" s="9"/>
       <x:c r="F39" s="10"/>
       <x:c r="G39" s="11"/>
+      <x:c r="H39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="9"/>
@@ -1294,6 +1398,7 @@
       <x:c r="E40" s="9"/>
       <x:c r="F40" s="10"/>
       <x:c r="G40" s="11"/>
+      <x:c r="H40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="9"/>
@@ -1303,6 +1408,7 @@
       <x:c r="E41" s="9"/>
       <x:c r="F41" s="10"/>
       <x:c r="G41" s="11"/>
+      <x:c r="H41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="9"/>
@@ -1312,6 +1418,7 @@
       <x:c r="E42" s="9"/>
       <x:c r="F42" s="10"/>
       <x:c r="G42" s="11"/>
+      <x:c r="H42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="9"/>
@@ -1321,6 +1428,7 @@
       <x:c r="E43" s="9"/>
       <x:c r="F43" s="10"/>
       <x:c r="G43" s="11"/>
+      <x:c r="H43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="9"/>
@@ -1330,6 +1438,7 @@
       <x:c r="E44" s="9"/>
       <x:c r="F44" s="10"/>
       <x:c r="G44" s="11"/>
+      <x:c r="H44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="9"/>
@@ -1339,6 +1448,7 @@
       <x:c r="E45" s="9"/>
       <x:c r="F45" s="10"/>
       <x:c r="G45" s="11"/>
+      <x:c r="H45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="9"/>
@@ -1348,6 +1458,7 @@
       <x:c r="E46" s="9"/>
       <x:c r="F46" s="10"/>
       <x:c r="G46" s="11"/>
+      <x:c r="H46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="9"/>
@@ -1357,6 +1468,7 @@
       <x:c r="E47" s="9"/>
       <x:c r="F47" s="10"/>
       <x:c r="G47" s="11"/>
+      <x:c r="H47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="9"/>
@@ -1366,6 +1478,7 @@
       <x:c r="E48" s="9"/>
       <x:c r="F48" s="10"/>
       <x:c r="G48" s="11"/>
+      <x:c r="H48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="9"/>
@@ -1375,6 +1488,7 @@
       <x:c r="E49" s="9"/>
       <x:c r="F49" s="10"/>
       <x:c r="G49" s="11"/>
+      <x:c r="H49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="9"/>
@@ -1384,6 +1498,7 @@
       <x:c r="E50" s="9"/>
       <x:c r="F50" s="10"/>
       <x:c r="G50" s="11"/>
+      <x:c r="H50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="9"/>
@@ -1393,6 +1508,7 @@
       <x:c r="E51" s="9"/>
       <x:c r="F51" s="10"/>
       <x:c r="G51" s="11"/>
+      <x:c r="H51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="9"/>
@@ -1402,6 +1518,7 @@
       <x:c r="E52" s="9"/>
       <x:c r="F52" s="10"/>
       <x:c r="G52" s="11"/>
+      <x:c r="H52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="9"/>
@@ -1411,6 +1528,7 @@
       <x:c r="E53" s="9"/>
       <x:c r="F53" s="10"/>
       <x:c r="G53" s="11"/>
+      <x:c r="H53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="9"/>
@@ -1420,6 +1538,7 @@
       <x:c r="E54" s="9"/>
       <x:c r="F54" s="10"/>
       <x:c r="G54" s="11"/>
+      <x:c r="H54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="9"/>
@@ -1429,6 +1548,7 @@
       <x:c r="E55" s="9"/>
       <x:c r="F55" s="10"/>
       <x:c r="G55" s="11"/>
+      <x:c r="H55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="9"/>
@@ -1438,6 +1558,7 @@
       <x:c r="E56" s="9"/>
       <x:c r="F56" s="10"/>
       <x:c r="G56" s="11"/>
+      <x:c r="H56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="9"/>
@@ -1447,6 +1568,7 @@
       <x:c r="E57" s="9"/>
       <x:c r="F57" s="10"/>
       <x:c r="G57" s="11"/>
+      <x:c r="H57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="9"/>
@@ -1456,6 +1578,7 @@
       <x:c r="E58" s="9"/>
       <x:c r="F58" s="10"/>
       <x:c r="G58" s="11"/>
+      <x:c r="H58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="9"/>
@@ -1465,6 +1588,7 @@
       <x:c r="E59" s="9"/>
       <x:c r="F59" s="10"/>
       <x:c r="G59" s="11"/>
+      <x:c r="H59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="9"/>
@@ -1474,6 +1598,7 @@
       <x:c r="E60" s="9"/>
       <x:c r="F60" s="10"/>
       <x:c r="G60" s="11"/>
+      <x:c r="H60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="9"/>
@@ -1483,6 +1608,7 @@
       <x:c r="E61" s="9"/>
       <x:c r="F61" s="10"/>
       <x:c r="G61" s="11"/>
+      <x:c r="H61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="9"/>
@@ -1492,6 +1618,7 @@
       <x:c r="E62" s="9"/>
       <x:c r="F62" s="10"/>
       <x:c r="G62" s="11"/>
+      <x:c r="H62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="9"/>
@@ -1501,6 +1628,7 @@
       <x:c r="E63" s="9"/>
       <x:c r="F63" s="10"/>
       <x:c r="G63" s="11"/>
+      <x:c r="H63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="9"/>
@@ -1510,6 +1638,7 @@
       <x:c r="E64" s="9"/>
       <x:c r="F64" s="10"/>
       <x:c r="G64" s="11"/>
+      <x:c r="H64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="9"/>
@@ -1519,6 +1648,7 @@
       <x:c r="E65" s="9"/>
       <x:c r="F65" s="10"/>
       <x:c r="G65" s="11"/>
+      <x:c r="H65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="9"/>
@@ -1528,6 +1658,7 @@
       <x:c r="E66" s="9"/>
       <x:c r="F66" s="10"/>
       <x:c r="G66" s="11"/>
+      <x:c r="H66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="9"/>
@@ -1537,6 +1668,7 @@
       <x:c r="E67" s="9"/>
       <x:c r="F67" s="10"/>
       <x:c r="G67" s="11"/>
+      <x:c r="H67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="9"/>
@@ -1546,6 +1678,7 @@
       <x:c r="E68" s="9"/>
       <x:c r="F68" s="10"/>
       <x:c r="G68" s="11"/>
+      <x:c r="H68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="9"/>
@@ -1555,6 +1688,7 @@
       <x:c r="E69" s="9"/>
       <x:c r="F69" s="10"/>
       <x:c r="G69" s="11"/>
+      <x:c r="H69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="9"/>
@@ -1564,6 +1698,7 @@
       <x:c r="E70" s="9"/>
       <x:c r="F70" s="10"/>
       <x:c r="G70" s="11"/>
+      <x:c r="H70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="9"/>
@@ -1573,6 +1708,7 @@
       <x:c r="E71" s="9"/>
       <x:c r="F71" s="10"/>
       <x:c r="G71" s="11"/>
+      <x:c r="H71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="9"/>
@@ -1582,6 +1718,7 @@
       <x:c r="E72" s="9"/>
       <x:c r="F72" s="10"/>
       <x:c r="G72" s="11"/>
+      <x:c r="H72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="9"/>
@@ -1591,6 +1728,7 @@
       <x:c r="E73" s="9"/>
       <x:c r="F73" s="10"/>
       <x:c r="G73" s="11"/>
+      <x:c r="H73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="9"/>
@@ -1600,6 +1738,7 @@
       <x:c r="E74" s="9"/>
       <x:c r="F74" s="10"/>
       <x:c r="G74" s="11"/>
+      <x:c r="H74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="9"/>
@@ -1609,6 +1748,7 @@
       <x:c r="E75" s="9"/>
       <x:c r="F75" s="10"/>
       <x:c r="G75" s="11"/>
+      <x:c r="H75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="9"/>
@@ -1618,6 +1758,7 @@
       <x:c r="E76" s="9"/>
       <x:c r="F76" s="10"/>
       <x:c r="G76" s="11"/>
+      <x:c r="H76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="9"/>
@@ -1627,6 +1768,7 @@
       <x:c r="E77" s="9"/>
       <x:c r="F77" s="10"/>
       <x:c r="G77" s="11"/>
+      <x:c r="H77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="9"/>
@@ -1636,6 +1778,7 @@
       <x:c r="E78" s="9"/>
       <x:c r="F78" s="10"/>
       <x:c r="G78" s="11"/>
+      <x:c r="H78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="9"/>
@@ -1645,6 +1788,7 @@
       <x:c r="E79" s="9"/>
       <x:c r="F79" s="10"/>
       <x:c r="G79" s="11"/>
+      <x:c r="H79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="9"/>
@@ -1654,6 +1798,7 @@
       <x:c r="E80" s="9"/>
       <x:c r="F80" s="10"/>
       <x:c r="G80" s="11"/>
+      <x:c r="H80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="9"/>
@@ -1663,6 +1808,7 @@
       <x:c r="E81" s="9"/>
       <x:c r="F81" s="10"/>
       <x:c r="G81" s="11"/>
+      <x:c r="H81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="9"/>
@@ -1672,6 +1818,7 @@
       <x:c r="E82" s="9"/>
       <x:c r="F82" s="10"/>
       <x:c r="G82" s="11"/>
+      <x:c r="H82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="9"/>
@@ -1681,6 +1828,7 @@
       <x:c r="E83" s="9"/>
       <x:c r="F83" s="10"/>
       <x:c r="G83" s="11"/>
+      <x:c r="H83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="9"/>
@@ -1690,6 +1838,7 @@
       <x:c r="E84" s="9"/>
       <x:c r="F84" s="10"/>
       <x:c r="G84" s="11"/>
+      <x:c r="H84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="9"/>
@@ -1699,6 +1848,7 @@
       <x:c r="E85" s="9"/>
       <x:c r="F85" s="10"/>
       <x:c r="G85" s="11"/>
+      <x:c r="H85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="9"/>
@@ -1708,6 +1858,7 @@
       <x:c r="E86" s="9"/>
       <x:c r="F86" s="10"/>
       <x:c r="G86" s="11"/>
+      <x:c r="H86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="9"/>
@@ -1717,6 +1868,7 @@
       <x:c r="E87" s="9"/>
       <x:c r="F87" s="10"/>
       <x:c r="G87" s="11"/>
+      <x:c r="H87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="9"/>
@@ -1726,6 +1878,7 @@
       <x:c r="E88" s="9"/>
       <x:c r="F88" s="10"/>
       <x:c r="G88" s="11"/>
+      <x:c r="H88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="9"/>
@@ -1735,6 +1888,7 @@
       <x:c r="E89" s="9"/>
       <x:c r="F89" s="10"/>
       <x:c r="G89" s="11"/>
+      <x:c r="H89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="9"/>
@@ -1744,6 +1898,7 @@
       <x:c r="E90" s="9"/>
       <x:c r="F90" s="10"/>
       <x:c r="G90" s="11"/>
+      <x:c r="H90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="9"/>
@@ -1753,6 +1908,7 @@
       <x:c r="E91" s="9"/>
       <x:c r="F91" s="10"/>
       <x:c r="G91" s="11"/>
+      <x:c r="H91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="9"/>
@@ -1762,6 +1918,7 @@
       <x:c r="E92" s="9"/>
       <x:c r="F92" s="10"/>
       <x:c r="G92" s="11"/>
+      <x:c r="H92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="9"/>
@@ -1771,6 +1928,7 @@
       <x:c r="E93" s="9"/>
       <x:c r="F93" s="10"/>
       <x:c r="G93" s="11"/>
+      <x:c r="H93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="9"/>
@@ -1780,6 +1938,7 @@
       <x:c r="E94" s="9"/>
       <x:c r="F94" s="10"/>
       <x:c r="G94" s="11"/>
+      <x:c r="H94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="9"/>
@@ -1789,6 +1948,7 @@
       <x:c r="E95" s="9"/>
       <x:c r="F95" s="10"/>
       <x:c r="G95" s="11"/>
+      <x:c r="H95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="9"/>
@@ -1798,6 +1958,7 @@
       <x:c r="E96" s="9"/>
       <x:c r="F96" s="10"/>
       <x:c r="G96" s="11"/>
+      <x:c r="H96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="9"/>
@@ -1807,6 +1968,7 @@
       <x:c r="E97" s="9"/>
       <x:c r="F97" s="10"/>
       <x:c r="G97" s="11"/>
+      <x:c r="H97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="9"/>
@@ -1816,6 +1978,7 @@
       <x:c r="E98" s="9"/>
       <x:c r="F98" s="10"/>
       <x:c r="G98" s="11"/>
+      <x:c r="H98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="9"/>
@@ -1825,6 +1988,7 @@
       <x:c r="E99" s="9"/>
       <x:c r="F99" s="10"/>
       <x:c r="G99" s="11"/>
+      <x:c r="H99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="9"/>
@@ -1834,6 +1998,7 @@
       <x:c r="E100" s="9"/>
       <x:c r="F100" s="10"/>
       <x:c r="G100" s="11"/>
+      <x:c r="H100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="9"/>
@@ -1843,6 +2008,7 @@
       <x:c r="E101" s="9"/>
       <x:c r="F101" s="10"/>
       <x:c r="G101" s="11"/>
+      <x:c r="H101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="9"/>
@@ -1852,6 +2018,7 @@
       <x:c r="E102" s="9"/>
       <x:c r="F102" s="10"/>
       <x:c r="G102" s="11"/>
+      <x:c r="H102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="9"/>
@@ -1861,6 +2028,7 @@
       <x:c r="E103" s="9"/>
       <x:c r="F103" s="10"/>
       <x:c r="G103" s="11"/>
+      <x:c r="H103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="9"/>
@@ -1870,6 +2038,7 @@
       <x:c r="E104" s="9"/>
       <x:c r="F104" s="10"/>
       <x:c r="G104" s="11"/>
+      <x:c r="H104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="9"/>
@@ -1879,6 +2048,7 @@
       <x:c r="E105" s="9"/>
       <x:c r="F105" s="10"/>
       <x:c r="G105" s="11"/>
+      <x:c r="H105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="9"/>
@@ -1888,6 +2058,7 @@
       <x:c r="E106" s="9"/>
       <x:c r="F106" s="10"/>
       <x:c r="G106" s="11"/>
+      <x:c r="H106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="9"/>
@@ -1897,6 +2068,7 @@
       <x:c r="E107" s="9"/>
       <x:c r="F107" s="10"/>
       <x:c r="G107" s="11"/>
+      <x:c r="H107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="9"/>
@@ -1906,6 +2078,7 @@
       <x:c r="E108" s="9"/>
       <x:c r="F108" s="10"/>
       <x:c r="G108" s="11"/>
+      <x:c r="H108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="9"/>
@@ -1915,6 +2088,7 @@
       <x:c r="E109" s="9"/>
       <x:c r="F109" s="10"/>
       <x:c r="G109" s="11"/>
+      <x:c r="H109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="9"/>
@@ -1924,6 +2098,7 @@
       <x:c r="E110" s="9"/>
       <x:c r="F110" s="10"/>
       <x:c r="G110" s="11"/>
+      <x:c r="H110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="9"/>
@@ -1933,6 +2108,7 @@
       <x:c r="E111" s="9"/>
       <x:c r="F111" s="10"/>
       <x:c r="G111" s="11"/>
+      <x:c r="H111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="9"/>
@@ -1942,6 +2118,7 @@
       <x:c r="E112" s="9"/>
       <x:c r="F112" s="10"/>
       <x:c r="G112" s="11"/>
+      <x:c r="H112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="9"/>
@@ -1951,6 +2128,7 @@
       <x:c r="E113" s="9"/>
       <x:c r="F113" s="10"/>
       <x:c r="G113" s="11"/>
+      <x:c r="H113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="9"/>
@@ -1960,6 +2138,7 @@
       <x:c r="E114" s="9"/>
       <x:c r="F114" s="10"/>
       <x:c r="G114" s="11"/>
+      <x:c r="H114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="9"/>
@@ -1969,6 +2148,7 @@
       <x:c r="E115" s="9"/>
       <x:c r="F115" s="10"/>
       <x:c r="G115" s="11"/>
+      <x:c r="H115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="9"/>
@@ -1978,6 +2158,7 @@
       <x:c r="E116" s="9"/>
       <x:c r="F116" s="10"/>
       <x:c r="G116" s="11"/>
+      <x:c r="H116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="9"/>
@@ -1987,6 +2168,7 @@
       <x:c r="E117" s="9"/>
       <x:c r="F117" s="10"/>
       <x:c r="G117" s="11"/>
+      <x:c r="H117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="9"/>
@@ -1996,6 +2178,7 @@
       <x:c r="E118" s="9"/>
       <x:c r="F118" s="10"/>
       <x:c r="G118" s="11"/>
+      <x:c r="H118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="9"/>
@@ -2005,6 +2188,7 @@
       <x:c r="E119" s="9"/>
       <x:c r="F119" s="10"/>
       <x:c r="G119" s="11"/>
+      <x:c r="H119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="9"/>
@@ -2014,6 +2198,7 @@
       <x:c r="E120" s="9"/>
       <x:c r="F120" s="10"/>
       <x:c r="G120" s="11"/>
+      <x:c r="H120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="9"/>
@@ -2023,6 +2208,7 @@
       <x:c r="E121" s="9"/>
       <x:c r="F121" s="10"/>
       <x:c r="G121" s="11"/>
+      <x:c r="H121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="9"/>
@@ -2032,6 +2218,7 @@
       <x:c r="E122" s="9"/>
       <x:c r="F122" s="10"/>
       <x:c r="G122" s="11"/>
+      <x:c r="H122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="9"/>
@@ -2041,6 +2228,7 @@
       <x:c r="E123" s="9"/>
       <x:c r="F123" s="10"/>
       <x:c r="G123" s="11"/>
+      <x:c r="H123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="9"/>
@@ -2050,6 +2238,7 @@
       <x:c r="E124" s="9"/>
       <x:c r="F124" s="10"/>
       <x:c r="G124" s="11"/>
+      <x:c r="H124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="9"/>
@@ -2059,6 +2248,7 @@
       <x:c r="E125" s="9"/>
       <x:c r="F125" s="10"/>
       <x:c r="G125" s="11"/>
+      <x:c r="H125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="9"/>
@@ -2068,6 +2258,7 @@
       <x:c r="E126" s="9"/>
       <x:c r="F126" s="10"/>
       <x:c r="G126" s="11"/>
+      <x:c r="H126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="9"/>
@@ -2077,6 +2268,7 @@
       <x:c r="E127" s="9"/>
       <x:c r="F127" s="10"/>
       <x:c r="G127" s="11"/>
+      <x:c r="H127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="9"/>
@@ -2086,6 +2278,7 @@
       <x:c r="E128" s="9"/>
       <x:c r="F128" s="10"/>
       <x:c r="G128" s="11"/>
+      <x:c r="H128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="9"/>
@@ -2095,6 +2288,7 @@
       <x:c r="E129" s="9"/>
       <x:c r="F129" s="10"/>
       <x:c r="G129" s="11"/>
+      <x:c r="H129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="9"/>
@@ -2104,6 +2298,7 @@
       <x:c r="E130" s="9"/>
       <x:c r="F130" s="10"/>
       <x:c r="G130" s="11"/>
+      <x:c r="H130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="9"/>
@@ -2113,6 +2308,7 @@
       <x:c r="E131" s="9"/>
       <x:c r="F131" s="10"/>
       <x:c r="G131" s="11"/>
+      <x:c r="H131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="9"/>
@@ -2122,6 +2318,7 @@
       <x:c r="E132" s="9"/>
       <x:c r="F132" s="10"/>
       <x:c r="G132" s="11"/>
+      <x:c r="H132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="9"/>
@@ -2131,6 +2328,7 @@
       <x:c r="E133" s="9"/>
       <x:c r="F133" s="10"/>
       <x:c r="G133" s="11"/>
+      <x:c r="H133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="9"/>
@@ -2140,6 +2338,7 @@
       <x:c r="E134" s="9"/>
       <x:c r="F134" s="10"/>
       <x:c r="G134" s="11"/>
+      <x:c r="H134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="9"/>
@@ -2149,6 +2348,7 @@
       <x:c r="E135" s="9"/>
       <x:c r="F135" s="10"/>
       <x:c r="G135" s="11"/>
+      <x:c r="H135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="9"/>
@@ -2158,6 +2358,7 @@
       <x:c r="E136" s="9"/>
       <x:c r="F136" s="10"/>
       <x:c r="G136" s="11"/>
+      <x:c r="H136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="9"/>
@@ -2167,6 +2368,7 @@
       <x:c r="E137" s="9"/>
       <x:c r="F137" s="10"/>
       <x:c r="G137" s="11"/>
+      <x:c r="H137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="9"/>
@@ -2176,6 +2378,7 @@
       <x:c r="E138" s="9"/>
       <x:c r="F138" s="10"/>
       <x:c r="G138" s="11"/>
+      <x:c r="H138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="9"/>
@@ -2185,6 +2388,7 @@
       <x:c r="E139" s="9"/>
       <x:c r="F139" s="10"/>
       <x:c r="G139" s="11"/>
+      <x:c r="H139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="9"/>
@@ -2194,6 +2398,7 @@
       <x:c r="E140" s="9"/>
       <x:c r="F140" s="10"/>
       <x:c r="G140" s="11"/>
+      <x:c r="H140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="9"/>
@@ -2203,6 +2408,7 @@
       <x:c r="E141" s="9"/>
       <x:c r="F141" s="10"/>
       <x:c r="G141" s="11"/>
+      <x:c r="H141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="9"/>
@@ -2212,6 +2418,7 @@
       <x:c r="E142" s="9"/>
       <x:c r="F142" s="10"/>
       <x:c r="G142" s="11"/>
+      <x:c r="H142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="9"/>
@@ -2221,6 +2428,7 @@
       <x:c r="E143" s="9"/>
       <x:c r="F143" s="10"/>
       <x:c r="G143" s="11"/>
+      <x:c r="H143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="9"/>
@@ -2230,6 +2438,7 @@
       <x:c r="E144" s="9"/>
       <x:c r="F144" s="10"/>
       <x:c r="G144" s="11"/>
+      <x:c r="H144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="9"/>
@@ -2239,6 +2448,7 @@
       <x:c r="E145" s="9"/>
       <x:c r="F145" s="10"/>
       <x:c r="G145" s="11"/>
+      <x:c r="H145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="9"/>
@@ -2248,6 +2458,7 @@
       <x:c r="E146" s="9"/>
       <x:c r="F146" s="10"/>
       <x:c r="G146" s="11"/>
+      <x:c r="H146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="9"/>
@@ -2257,6 +2468,7 @@
       <x:c r="E147" s="9"/>
       <x:c r="F147" s="10"/>
       <x:c r="G147" s="11"/>
+      <x:c r="H147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="9"/>
@@ -2266,6 +2478,7 @@
       <x:c r="E148" s="9"/>
       <x:c r="F148" s="10"/>
       <x:c r="G148" s="11"/>
+      <x:c r="H148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="9"/>
@@ -2275,6 +2488,7 @@
       <x:c r="E149" s="9"/>
       <x:c r="F149" s="10"/>
       <x:c r="G149" s="11"/>
+      <x:c r="H149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="9"/>
@@ -2284,6 +2498,7 @@
       <x:c r="E150" s="9"/>
       <x:c r="F150" s="10"/>
       <x:c r="G150" s="11"/>
+      <x:c r="H150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="9"/>
@@ -2293,6 +2508,7 @@
       <x:c r="E151" s="9"/>
       <x:c r="F151" s="10"/>
       <x:c r="G151" s="11"/>
+      <x:c r="H151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="9"/>
@@ -2302,6 +2518,7 @@
       <x:c r="E152" s="9"/>
       <x:c r="F152" s="10"/>
       <x:c r="G152" s="11"/>
+      <x:c r="H152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="9"/>
@@ -2311,6 +2528,7 @@
       <x:c r="E153" s="9"/>
       <x:c r="F153" s="10"/>
       <x:c r="G153" s="11"/>
+      <x:c r="H153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="9"/>
@@ -2320,6 +2538,7 @@
       <x:c r="E154" s="9"/>
       <x:c r="F154" s="10"/>
       <x:c r="G154" s="11"/>
+      <x:c r="H154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="9"/>
@@ -2329,6 +2548,7 @@
       <x:c r="E155" s="9"/>
       <x:c r="F155" s="10"/>
       <x:c r="G155" s="11"/>
+      <x:c r="H155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="9"/>
@@ -2338,6 +2558,7 @@
       <x:c r="E156" s="9"/>
       <x:c r="F156" s="10"/>
       <x:c r="G156" s="11"/>
+      <x:c r="H156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="9"/>
@@ -2347,6 +2568,7 @@
       <x:c r="E157" s="9"/>
       <x:c r="F157" s="10"/>
       <x:c r="G157" s="11"/>
+      <x:c r="H157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="9"/>
@@ -2356,6 +2578,7 @@
       <x:c r="E158" s="9"/>
       <x:c r="F158" s="10"/>
       <x:c r="G158" s="11"/>
+      <x:c r="H158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="9"/>
@@ -2365,6 +2588,7 @@
       <x:c r="E159" s="9"/>
       <x:c r="F159" s="10"/>
       <x:c r="G159" s="11"/>
+      <x:c r="H159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="9"/>
@@ -2374,6 +2598,7 @@
       <x:c r="E160" s="9"/>
       <x:c r="F160" s="10"/>
       <x:c r="G160" s="11"/>
+      <x:c r="H160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="9"/>
@@ -2383,6 +2608,7 @@
       <x:c r="E161" s="9"/>
       <x:c r="F161" s="10"/>
       <x:c r="G161" s="11"/>
+      <x:c r="H161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="9"/>
@@ -2392,6 +2618,7 @@
       <x:c r="E162" s="9"/>
       <x:c r="F162" s="10"/>
       <x:c r="G162" s="11"/>
+      <x:c r="H162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="9"/>
@@ -2401,6 +2628,7 @@
       <x:c r="E163" s="9"/>
       <x:c r="F163" s="10"/>
       <x:c r="G163" s="11"/>
+      <x:c r="H163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="9"/>
@@ -2410,6 +2638,7 @@
       <x:c r="E164" s="9"/>
       <x:c r="F164" s="10"/>
       <x:c r="G164" s="11"/>
+      <x:c r="H164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="9"/>
@@ -2419,6 +2648,7 @@
       <x:c r="E165" s="9"/>
       <x:c r="F165" s="10"/>
       <x:c r="G165" s="11"/>
+      <x:c r="H165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="9"/>
@@ -2428,6 +2658,7 @@
       <x:c r="E166" s="9"/>
       <x:c r="F166" s="10"/>
       <x:c r="G166" s="11"/>
+      <x:c r="H166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="9"/>
@@ -2437,6 +2668,7 @@
       <x:c r="E167" s="9"/>
       <x:c r="F167" s="10"/>
       <x:c r="G167" s="11"/>
+      <x:c r="H167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="9"/>
@@ -2446,6 +2678,7 @@
       <x:c r="E168" s="9"/>
       <x:c r="F168" s="10"/>
       <x:c r="G168" s="11"/>
+      <x:c r="H168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="9"/>
@@ -2455,6 +2688,7 @@
       <x:c r="E169" s="9"/>
       <x:c r="F169" s="10"/>
       <x:c r="G169" s="11"/>
+      <x:c r="H169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="9"/>
@@ -2464,6 +2698,7 @@
       <x:c r="E170" s="9"/>
       <x:c r="F170" s="10"/>
       <x:c r="G170" s="11"/>
+      <x:c r="H170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="9"/>
@@ -2473,6 +2708,7 @@
       <x:c r="E171" s="9"/>
       <x:c r="F171" s="10"/>
       <x:c r="G171" s="11"/>
+      <x:c r="H171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="9"/>
@@ -2482,6 +2718,7 @@
       <x:c r="E172" s="9"/>
       <x:c r="F172" s="10"/>
       <x:c r="G172" s="11"/>
+      <x:c r="H172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="9"/>
@@ -2491,6 +2728,7 @@
       <x:c r="E173" s="9"/>
       <x:c r="F173" s="10"/>
       <x:c r="G173" s="11"/>
+      <x:c r="H173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="9"/>
@@ -2500,6 +2738,7 @@
       <x:c r="E174" s="9"/>
       <x:c r="F174" s="10"/>
       <x:c r="G174" s="11"/>
+      <x:c r="H174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="9"/>
@@ -2509,6 +2748,7 @@
       <x:c r="E175" s="9"/>
       <x:c r="F175" s="10"/>
       <x:c r="G175" s="11"/>
+      <x:c r="H175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="9"/>
@@ -2518,6 +2758,7 @@
       <x:c r="E176" s="9"/>
       <x:c r="F176" s="10"/>
       <x:c r="G176" s="11"/>
+      <x:c r="H176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="9"/>
@@ -2527,6 +2768,7 @@
       <x:c r="E177" s="9"/>
       <x:c r="F177" s="10"/>
       <x:c r="G177" s="11"/>
+      <x:c r="H177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="9"/>
@@ -2536,6 +2778,7 @@
       <x:c r="E178" s="9"/>
       <x:c r="F178" s="10"/>
       <x:c r="G178" s="11"/>
+      <x:c r="H178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="9"/>
@@ -2545,6 +2788,7 @@
       <x:c r="E179" s="9"/>
       <x:c r="F179" s="10"/>
       <x:c r="G179" s="11"/>
+      <x:c r="H179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="9"/>
@@ -2554,6 +2798,7 @@
       <x:c r="E180" s="9"/>
       <x:c r="F180" s="10"/>
       <x:c r="G180" s="11"/>
+      <x:c r="H180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="9"/>
@@ -2563,6 +2808,7 @@
       <x:c r="E181" s="9"/>
       <x:c r="F181" s="10"/>
       <x:c r="G181" s="11"/>
+      <x:c r="H181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="9"/>
@@ -2572,6 +2818,7 @@
       <x:c r="E182" s="9"/>
       <x:c r="F182" s="10"/>
       <x:c r="G182" s="11"/>
+      <x:c r="H182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="9"/>
@@ -2581,6 +2828,7 @@
       <x:c r="E183" s="9"/>
       <x:c r="F183" s="10"/>
       <x:c r="G183" s="11"/>
+      <x:c r="H183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="9"/>
@@ -2590,6 +2838,7 @@
       <x:c r="E184" s="9"/>
       <x:c r="F184" s="10"/>
       <x:c r="G184" s="11"/>
+      <x:c r="H184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="9"/>
@@ -2599,6 +2848,7 @@
       <x:c r="E185" s="9"/>
       <x:c r="F185" s="10"/>
       <x:c r="G185" s="11"/>
+      <x:c r="H185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="9"/>
@@ -2608,6 +2858,7 @@
       <x:c r="E186" s="9"/>
       <x:c r="F186" s="10"/>
       <x:c r="G186" s="11"/>
+      <x:c r="H186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="9"/>
@@ -2617,6 +2868,7 @@
       <x:c r="E187" s="9"/>
       <x:c r="F187" s="10"/>
       <x:c r="G187" s="11"/>
+      <x:c r="H187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="9"/>
@@ -2626,6 +2878,7 @@
       <x:c r="E188" s="9"/>
       <x:c r="F188" s="10"/>
       <x:c r="G188" s="11"/>
+      <x:c r="H188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="9"/>
@@ -2635,6 +2888,7 @@
       <x:c r="E189" s="9"/>
       <x:c r="F189" s="10"/>
       <x:c r="G189" s="11"/>
+      <x:c r="H189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="9"/>
@@ -2644,6 +2898,7 @@
       <x:c r="E190" s="9"/>
       <x:c r="F190" s="10"/>
       <x:c r="G190" s="11"/>
+      <x:c r="H190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="9"/>
@@ -2653,6 +2908,7 @@
       <x:c r="E191" s="9"/>
       <x:c r="F191" s="10"/>
       <x:c r="G191" s="11"/>
+      <x:c r="H191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="9"/>
@@ -2662,6 +2918,7 @@
       <x:c r="E192" s="9"/>
       <x:c r="F192" s="10"/>
       <x:c r="G192" s="11"/>
+      <x:c r="H192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="9"/>
@@ -2671,6 +2928,7 @@
       <x:c r="E193" s="9"/>
       <x:c r="F193" s="10"/>
       <x:c r="G193" s="11"/>
+      <x:c r="H193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="9"/>
@@ -2680,6 +2938,7 @@
       <x:c r="E194" s="9"/>
       <x:c r="F194" s="10"/>
       <x:c r="G194" s="11"/>
+      <x:c r="H194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="9"/>
@@ -2689,6 +2948,7 @@
       <x:c r="E195" s="9"/>
       <x:c r="F195" s="10"/>
       <x:c r="G195" s="11"/>
+      <x:c r="H195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="9"/>
@@ -2698,6 +2958,7 @@
       <x:c r="E196" s="9"/>
       <x:c r="F196" s="10"/>
       <x:c r="G196" s="11"/>
+      <x:c r="H196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="9"/>
@@ -2707,6 +2968,7 @@
       <x:c r="E197" s="9"/>
       <x:c r="F197" s="10"/>
       <x:c r="G197" s="11"/>
+      <x:c r="H197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="9"/>
@@ -2716,6 +2978,7 @@
       <x:c r="E198" s="9"/>
       <x:c r="F198" s="10"/>
       <x:c r="G198" s="11"/>
+      <x:c r="H198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="9"/>
@@ -2725,6 +2988,7 @@
       <x:c r="E199" s="9"/>
       <x:c r="F199" s="10"/>
       <x:c r="G199" s="11"/>
+      <x:c r="H199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="9"/>
@@ -2734,6 +2998,7 @@
       <x:c r="E200" s="9"/>
       <x:c r="F200" s="10"/>
       <x:c r="G200" s="11"/>
+      <x:c r="H200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="9"/>
@@ -2743,6 +3008,7 @@
       <x:c r="E201" s="9"/>
       <x:c r="F201" s="10"/>
       <x:c r="G201" s="11"/>
+      <x:c r="H201"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="9"/>
@@ -2752,6 +3018,7 @@
       <x:c r="E202" s="9"/>
       <x:c r="F202" s="10"/>
       <x:c r="G202" s="11"/>
+      <x:c r="H202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="9"/>
@@ -2761,6 +3028,7 @@
       <x:c r="E203" s="9"/>
       <x:c r="F203" s="10"/>
       <x:c r="G203" s="11"/>
+      <x:c r="H203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="9"/>
@@ -2770,13 +3038,14 @@
       <x:c r="E204" s="9"/>
       <x:c r="F204" s="10"/>
       <x:c r="G204" s="11"/>
+      <x:c r="H204"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:dataValidations count="6">
+  <x:dataValidations count="7">
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="Sole Type" error="Choose one of: EVA, PVC, PU, STUCK-ON" sqref="B10:B204">
       <x:formula1>"EVA,PVC,PU,STUCK-ON"</x:formula1>
     </x:dataValidation>
@@ -2795,6 +3064,9 @@
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="UOM" error="Choose one of: PAIR, MTR, CM, KG, GRAM, PCS, SHEET, LTR. Keep the same unit for a material everywhere." sqref="F5:F204">
       <x:formula1>"PAIR,MTR,CM,KG,GRAM,PCS,SHEET,LTR"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="H5:H204">
+      <x:formula1>"Small,Large"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2808,639 +3080,1003 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" customWidth="1"/>
-    <x:col min="2" max="2" width="15" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
     </x:row>
-    <x:row r="2" ht="16" customHeight="1">
-      <x:c r="A2" s="7" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="34" t="str">
+        <x:v>Size Range may be a combo or one size. Write S/L where available. For a standalone size, BOM Range tells Factory OS which BOM and carton context it uses.</x:v>
+      </x:c>
+      <x:c r="B2" s="34"/>
+      <x:c r="C2" s="34"/>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>Size Range or Individual Size</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D4" s="45" t="str">
+        <x:v>BOM Range (optional)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="9"/>
       <x:c r="B5" s="9"/>
       <x:c r="C5" s="12"/>
+      <x:c r="D5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="9"/>
       <x:c r="B6" s="9"/>
       <x:c r="C6" s="12"/>
+      <x:c r="D6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="9"/>
       <x:c r="B7" s="9"/>
       <x:c r="C7" s="12"/>
+      <x:c r="D7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="9"/>
       <x:c r="B8" s="9"/>
       <x:c r="C8" s="12"/>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="9"/>
       <x:c r="B9" s="9"/>
       <x:c r="C9" s="12"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="9"/>
       <x:c r="B10" s="9"/>
       <x:c r="C10" s="12"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="9"/>
       <x:c r="B11" s="9"/>
       <x:c r="C11" s="12"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9"/>
       <x:c r="B12" s="9"/>
       <x:c r="C12" s="12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9"/>
       <x:c r="B13" s="9"/>
       <x:c r="C13" s="12"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="12"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="12"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="12"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="12"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="12"/>
+      <x:c r="D18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="12"/>
+      <x:c r="D19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="12"/>
+      <x:c r="D20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="12"/>
+      <x:c r="D21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="12"/>
+      <x:c r="D22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="9"/>
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="12"/>
+      <x:c r="D23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="9"/>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="12"/>
+      <x:c r="D24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="9"/>
       <x:c r="C25" s="12"/>
+      <x:c r="D25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="9"/>
       <x:c r="B26" s="9"/>
       <x:c r="C26" s="12"/>
+      <x:c r="D26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9"/>
       <x:c r="B27" s="9"/>
       <x:c r="C27" s="12"/>
+      <x:c r="D27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="9"/>
       <x:c r="B28" s="9"/>
       <x:c r="C28" s="12"/>
+      <x:c r="D28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="9"/>
       <x:c r="B29" s="9"/>
       <x:c r="C29" s="12"/>
+      <x:c r="D29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="9"/>
       <x:c r="B30" s="9"/>
       <x:c r="C30" s="12"/>
+      <x:c r="D30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="9"/>
       <x:c r="B31" s="9"/>
       <x:c r="C31" s="12"/>
+      <x:c r="D31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="9"/>
       <x:c r="B32" s="9"/>
       <x:c r="C32" s="12"/>
+      <x:c r="D32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9"/>
       <x:c r="B33" s="9"/>
       <x:c r="C33" s="12"/>
+      <x:c r="D33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="9"/>
       <x:c r="C34" s="12"/>
+      <x:c r="D34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9"/>
       <x:c r="B35" s="9"/>
       <x:c r="C35" s="12"/>
+      <x:c r="D35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="9"/>
       <x:c r="B36" s="9"/>
       <x:c r="C36" s="12"/>
+      <x:c r="D36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="9"/>
       <x:c r="B37" s="9"/>
       <x:c r="C37" s="12"/>
+      <x:c r="D37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="9"/>
       <x:c r="B38" s="9"/>
       <x:c r="C38" s="12"/>
+      <x:c r="D38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="9"/>
       <x:c r="B39" s="9"/>
       <x:c r="C39" s="12"/>
+      <x:c r="D39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="9"/>
       <x:c r="B40" s="9"/>
       <x:c r="C40" s="12"/>
+      <x:c r="D40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="9"/>
       <x:c r="B41" s="9"/>
       <x:c r="C41" s="12"/>
+      <x:c r="D41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="9"/>
       <x:c r="B42" s="9"/>
       <x:c r="C42" s="12"/>
+      <x:c r="D42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="9"/>
       <x:c r="B43" s="9"/>
       <x:c r="C43" s="12"/>
+      <x:c r="D43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="9"/>
       <x:c r="B44" s="9"/>
       <x:c r="C44" s="12"/>
+      <x:c r="D44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="9"/>
       <x:c r="B45" s="9"/>
       <x:c r="C45" s="12"/>
+      <x:c r="D45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="9"/>
       <x:c r="B46" s="9"/>
       <x:c r="C46" s="12"/>
+      <x:c r="D46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="9"/>
       <x:c r="B47" s="9"/>
       <x:c r="C47" s="12"/>
+      <x:c r="D47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="9"/>
       <x:c r="B48" s="9"/>
       <x:c r="C48" s="12"/>
+      <x:c r="D48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="9"/>
       <x:c r="B49" s="9"/>
       <x:c r="C49" s="12"/>
+      <x:c r="D49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="9"/>
       <x:c r="B50" s="9"/>
       <x:c r="C50" s="12"/>
+      <x:c r="D50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="9"/>
       <x:c r="B51" s="9"/>
       <x:c r="C51" s="12"/>
+      <x:c r="D51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="9"/>
       <x:c r="B52" s="9"/>
       <x:c r="C52" s="12"/>
+      <x:c r="D52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="9"/>
       <x:c r="B53" s="9"/>
       <x:c r="C53" s="12"/>
+      <x:c r="D53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="9"/>
       <x:c r="B54" s="9"/>
       <x:c r="C54" s="12"/>
+      <x:c r="D54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="9"/>
       <x:c r="B55" s="9"/>
       <x:c r="C55" s="12"/>
+      <x:c r="D55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="9"/>
       <x:c r="B56" s="9"/>
       <x:c r="C56" s="12"/>
+      <x:c r="D56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="9"/>
       <x:c r="B57" s="9"/>
       <x:c r="C57" s="12"/>
+      <x:c r="D57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="9"/>
       <x:c r="B58" s="9"/>
       <x:c r="C58" s="12"/>
+      <x:c r="D58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="9"/>
       <x:c r="B59" s="9"/>
       <x:c r="C59" s="12"/>
+      <x:c r="D59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="9"/>
       <x:c r="B60" s="9"/>
       <x:c r="C60" s="12"/>
+      <x:c r="D60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="9"/>
       <x:c r="B61" s="9"/>
       <x:c r="C61" s="12"/>
+      <x:c r="D61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="9"/>
       <x:c r="B62" s="9"/>
       <x:c r="C62" s="12"/>
+      <x:c r="D62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="9"/>
       <x:c r="B63" s="9"/>
       <x:c r="C63" s="12"/>
+      <x:c r="D63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="9"/>
       <x:c r="B64" s="9"/>
       <x:c r="C64" s="12"/>
+      <x:c r="D64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="9"/>
       <x:c r="B65" s="9"/>
       <x:c r="C65" s="12"/>
+      <x:c r="D65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="9"/>
       <x:c r="B66" s="9"/>
       <x:c r="C66" s="12"/>
+      <x:c r="D66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="9"/>
       <x:c r="B67" s="9"/>
       <x:c r="C67" s="12"/>
+      <x:c r="D67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="9"/>
       <x:c r="B68" s="9"/>
       <x:c r="C68" s="12"/>
+      <x:c r="D68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="9"/>
       <x:c r="B69" s="9"/>
       <x:c r="C69" s="12"/>
+      <x:c r="D69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="9"/>
       <x:c r="B70" s="9"/>
       <x:c r="C70" s="12"/>
+      <x:c r="D70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="9"/>
       <x:c r="B71" s="9"/>
       <x:c r="C71" s="12"/>
+      <x:c r="D71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="9"/>
       <x:c r="B72" s="9"/>
       <x:c r="C72" s="12"/>
+      <x:c r="D72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="9"/>
       <x:c r="B73" s="9"/>
       <x:c r="C73" s="12"/>
+      <x:c r="D73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="9"/>
       <x:c r="B74" s="9"/>
       <x:c r="C74" s="12"/>
+      <x:c r="D74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="9"/>
       <x:c r="B75" s="9"/>
       <x:c r="C75" s="12"/>
+      <x:c r="D75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="9"/>
       <x:c r="B76" s="9"/>
       <x:c r="C76" s="12"/>
+      <x:c r="D76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="9"/>
       <x:c r="B77" s="9"/>
       <x:c r="C77" s="12"/>
+      <x:c r="D77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="9"/>
       <x:c r="B78" s="9"/>
       <x:c r="C78" s="12"/>
+      <x:c r="D78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="9"/>
       <x:c r="B79" s="9"/>
       <x:c r="C79" s="12"/>
+      <x:c r="D79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="9"/>
       <x:c r="B80" s="9"/>
       <x:c r="C80" s="12"/>
+      <x:c r="D80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="9"/>
       <x:c r="B81" s="9"/>
       <x:c r="C81" s="12"/>
+      <x:c r="D81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="9"/>
       <x:c r="B82" s="9"/>
       <x:c r="C82" s="12"/>
+      <x:c r="D82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="9"/>
       <x:c r="B83" s="9"/>
       <x:c r="C83" s="12"/>
+      <x:c r="D83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="9"/>
       <x:c r="B84" s="9"/>
       <x:c r="C84" s="12"/>
+      <x:c r="D84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="9"/>
       <x:c r="B85" s="9"/>
       <x:c r="C85" s="12"/>
+      <x:c r="D85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="9"/>
       <x:c r="B86" s="9"/>
       <x:c r="C86" s="12"/>
+      <x:c r="D86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="9"/>
       <x:c r="B87" s="9"/>
       <x:c r="C87" s="12"/>
+      <x:c r="D87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="9"/>
       <x:c r="B88" s="9"/>
       <x:c r="C88" s="12"/>
+      <x:c r="D88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="9"/>
       <x:c r="B89" s="9"/>
       <x:c r="C89" s="12"/>
+      <x:c r="D89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="9"/>
       <x:c r="B90" s="9"/>
       <x:c r="C90" s="12"/>
+      <x:c r="D90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="9"/>
       <x:c r="B91" s="9"/>
       <x:c r="C91" s="12"/>
+      <x:c r="D91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="9"/>
       <x:c r="B92" s="9"/>
       <x:c r="C92" s="12"/>
+      <x:c r="D92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="9"/>
       <x:c r="B93" s="9"/>
       <x:c r="C93" s="12"/>
+      <x:c r="D93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="9"/>
       <x:c r="B94" s="9"/>
       <x:c r="C94" s="12"/>
+      <x:c r="D94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="9"/>
       <x:c r="B95" s="9"/>
       <x:c r="C95" s="12"/>
+      <x:c r="D95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="9"/>
       <x:c r="B96" s="9"/>
       <x:c r="C96" s="12"/>
+      <x:c r="D96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="9"/>
       <x:c r="B97" s="9"/>
       <x:c r="C97" s="12"/>
+      <x:c r="D97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="9"/>
       <x:c r="B98" s="9"/>
       <x:c r="C98" s="12"/>
+      <x:c r="D98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="9"/>
       <x:c r="B99" s="9"/>
       <x:c r="C99" s="12"/>
+      <x:c r="D99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="9"/>
       <x:c r="B100" s="9"/>
       <x:c r="C100" s="12"/>
+      <x:c r="D100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="9"/>
       <x:c r="B101" s="9"/>
       <x:c r="C101" s="12"/>
+      <x:c r="D101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="9"/>
       <x:c r="B102" s="9"/>
       <x:c r="C102" s="12"/>
+      <x:c r="D102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="9"/>
       <x:c r="B103" s="9"/>
       <x:c r="C103" s="12"/>
+      <x:c r="D103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="9"/>
       <x:c r="B104" s="9"/>
       <x:c r="C104" s="12"/>
+      <x:c r="D104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="9"/>
       <x:c r="B105" s="9"/>
       <x:c r="C105" s="12"/>
+      <x:c r="D105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="9"/>
       <x:c r="B106" s="9"/>
       <x:c r="C106" s="12"/>
+      <x:c r="D106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="9"/>
       <x:c r="B107" s="9"/>
       <x:c r="C107" s="12"/>
+      <x:c r="D107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="9"/>
       <x:c r="B108" s="9"/>
       <x:c r="C108" s="12"/>
+      <x:c r="D108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="9"/>
       <x:c r="B109" s="9"/>
       <x:c r="C109" s="12"/>
+      <x:c r="D109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="9"/>
       <x:c r="B110" s="9"/>
       <x:c r="C110" s="12"/>
+      <x:c r="D110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="9"/>
       <x:c r="B111" s="9"/>
       <x:c r="C111" s="12"/>
+      <x:c r="D111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="9"/>
       <x:c r="B112" s="9"/>
       <x:c r="C112" s="12"/>
+      <x:c r="D112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="9"/>
       <x:c r="B113" s="9"/>
       <x:c r="C113" s="12"/>
+      <x:c r="D113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="9"/>
       <x:c r="B114" s="9"/>
       <x:c r="C114" s="12"/>
+      <x:c r="D114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="9"/>
       <x:c r="B115" s="9"/>
       <x:c r="C115" s="12"/>
+      <x:c r="D115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="9"/>
       <x:c r="B116" s="9"/>
       <x:c r="C116" s="12"/>
+      <x:c r="D116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="9"/>
       <x:c r="B117" s="9"/>
       <x:c r="C117" s="12"/>
+      <x:c r="D117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="9"/>
       <x:c r="B118" s="9"/>
       <x:c r="C118" s="12"/>
+      <x:c r="D118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="9"/>
       <x:c r="B119" s="9"/>
       <x:c r="C119" s="12"/>
+      <x:c r="D119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="9"/>
       <x:c r="B120" s="9"/>
       <x:c r="C120" s="12"/>
+      <x:c r="D120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="9"/>
       <x:c r="B121" s="9"/>
       <x:c r="C121" s="12"/>
+      <x:c r="D121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="9"/>
       <x:c r="B122" s="9"/>
       <x:c r="C122" s="12"/>
+      <x:c r="D122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="9"/>
       <x:c r="B123" s="9"/>
       <x:c r="C123" s="12"/>
+      <x:c r="D123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="9"/>
       <x:c r="B124" s="9"/>
       <x:c r="C124" s="12"/>
+      <x:c r="D124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="D125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="D126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="D127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="D128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="D129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="D130"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="D131"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="D132"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="D133"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="D134"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="D135"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="D136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="D137"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="D138"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="D139"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="D140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="D141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="D142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="D143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="D144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="D145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="D146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="D147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="D148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="D149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="D150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="D151"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="D152"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="D153"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="D154"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="D155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="D156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="D157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="D158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="D159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="D160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="D161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="D162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="D163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="D164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="D165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="D166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="D167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="D168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="D169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="D170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="D171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="D172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="D173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="D174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="D175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="D176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="D177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="D178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="D179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="D180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="D181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="D182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="D183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="D184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="D185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="D186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="D187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="D188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="D189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="D190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="D191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="D192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="D193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="D194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="D195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="D196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="D197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="D198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="D199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="D200"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="D201"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="D202"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="D203"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="D204"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3454,18 +4090,19 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" customWidth="1"/>
-    <x:col min="2" max="2" width="15" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" customWidth="1"/>
     <x:col min="4" max="4" width="15" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="15" customWidth="1"/>
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Catalogue — description, MRP by range, machine and packing source</x:v>
+        <x:v>Catalogue — details and optional MRP by range or size</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -3474,41 +4111,45 @@
       <x:c r="F1" s="6"/>
       <x:c r="G1" s="6"/>
     </x:row>
-    <x:row r="2" ht="16" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Repeat the exact Article Code. Packing Source is optional: blank = factory rule, SELF = own chart, or an existing article code.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="34" t="str">
+        <x:v>Repeat the exact Article Code. Size entries accept 7S/7L (also S7/L7). BOM Range is only needed when an individual size must borrow a particular range.</x:v>
+      </x:c>
+      <x:c r="B2" s="34"/>
+      <x:c r="C2" s="34"/>
+      <x:c r="D2" s="34"/>
+      <x:c r="E2" s="34"/>
+      <x:c r="F2" s="34"/>
+      <x:c r="G2" s="34"/>
+      <x:c r="H2" s="35"/>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>Size Range or Individual Size</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
         <x:v>Packing Source</x:v>
       </x:c>
       <x:c r="H4" s="31" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I4" s="45" t="str">
+        <x:v>BOM Range (optional)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3520,6 +4161,7 @@
       <x:c r="F5" s="9"/>
       <x:c r="G5" s="9"/>
       <x:c r="H5" s="32"/>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="9"/>
@@ -3530,6 +4172,7 @@
       <x:c r="F6" s="9"/>
       <x:c r="G6" s="9"/>
       <x:c r="H6" s="32"/>
+      <x:c r="I6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="9"/>
@@ -3540,6 +4183,7 @@
       <x:c r="F7" s="9"/>
       <x:c r="G7" s="9"/>
       <x:c r="H7" s="32"/>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="9"/>
@@ -3550,6 +4194,7 @@
       <x:c r="F8" s="9"/>
       <x:c r="G8" s="9"/>
       <x:c r="H8" s="32"/>
+      <x:c r="I8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="9"/>
@@ -3560,6 +4205,7 @@
       <x:c r="F9" s="9"/>
       <x:c r="G9" s="9"/>
       <x:c r="H9" s="32"/>
+      <x:c r="I9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="9"/>
@@ -3570,6 +4216,7 @@
       <x:c r="F10" s="9"/>
       <x:c r="G10" s="9"/>
       <x:c r="H10" s="32"/>
+      <x:c r="I10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="9"/>
@@ -3580,6 +4227,7 @@
       <x:c r="F11" s="9"/>
       <x:c r="G11" s="9"/>
       <x:c r="H11" s="32"/>
+      <x:c r="I11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9"/>
@@ -3590,6 +4238,7 @@
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="32"/>
+      <x:c r="I12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9"/>
@@ -3600,6 +4249,7 @@
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="32"/>
+      <x:c r="I13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9"/>
@@ -3610,6 +4260,7 @@
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="32"/>
+      <x:c r="I14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9"/>
@@ -3620,6 +4271,7 @@
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="32"/>
+      <x:c r="I15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9"/>
@@ -3630,6 +4282,7 @@
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="32"/>
+      <x:c r="I16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9"/>
@@ -3640,6 +4293,7 @@
       <x:c r="F17" s="9"/>
       <x:c r="G17" s="9"/>
       <x:c r="H17" s="32"/>
+      <x:c r="I17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="9"/>
@@ -3650,6 +4304,7 @@
       <x:c r="F18" s="9"/>
       <x:c r="G18" s="9"/>
       <x:c r="H18" s="32"/>
+      <x:c r="I18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9"/>
@@ -3660,6 +4315,7 @@
       <x:c r="F19" s="9"/>
       <x:c r="G19" s="9"/>
       <x:c r="H19" s="32"/>
+      <x:c r="I19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9"/>
@@ -3670,6 +4326,7 @@
       <x:c r="F20" s="9"/>
       <x:c r="G20" s="9"/>
       <x:c r="H20" s="32"/>
+      <x:c r="I20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9"/>
@@ -3680,6 +4337,7 @@
       <x:c r="F21" s="9"/>
       <x:c r="G21" s="9"/>
       <x:c r="H21" s="32"/>
+      <x:c r="I21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9"/>
@@ -3690,6 +4348,7 @@
       <x:c r="F22" s="9"/>
       <x:c r="G22" s="9"/>
       <x:c r="H22" s="32"/>
+      <x:c r="I22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="9"/>
@@ -3700,6 +4359,7 @@
       <x:c r="F23" s="9"/>
       <x:c r="G23" s="9"/>
       <x:c r="H23" s="32"/>
+      <x:c r="I23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="9"/>
@@ -3710,6 +4370,7 @@
       <x:c r="F24" s="9"/>
       <x:c r="G24" s="9"/>
       <x:c r="H24" s="32"/>
+      <x:c r="I24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="9"/>
@@ -3720,6 +4381,7 @@
       <x:c r="F25" s="9"/>
       <x:c r="G25" s="9"/>
       <x:c r="H25" s="32"/>
+      <x:c r="I25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="9"/>
@@ -3730,6 +4392,7 @@
       <x:c r="F26" s="9"/>
       <x:c r="G26" s="9"/>
       <x:c r="H26" s="32"/>
+      <x:c r="I26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9"/>
@@ -3740,6 +4403,7 @@
       <x:c r="F27" s="9"/>
       <x:c r="G27" s="9"/>
       <x:c r="H27" s="32"/>
+      <x:c r="I27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="9"/>
@@ -3750,6 +4414,7 @@
       <x:c r="F28" s="9"/>
       <x:c r="G28" s="9"/>
       <x:c r="H28" s="32"/>
+      <x:c r="I28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="9"/>
@@ -3760,6 +4425,7 @@
       <x:c r="F29" s="9"/>
       <x:c r="G29" s="9"/>
       <x:c r="H29" s="32"/>
+      <x:c r="I29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="9"/>
@@ -3770,6 +4436,7 @@
       <x:c r="F30" s="9"/>
       <x:c r="G30" s="9"/>
       <x:c r="H30" s="32"/>
+      <x:c r="I30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="9"/>
@@ -3780,6 +4447,7 @@
       <x:c r="F31" s="9"/>
       <x:c r="G31" s="9"/>
       <x:c r="H31" s="32"/>
+      <x:c r="I31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="9"/>
@@ -3790,6 +4458,7 @@
       <x:c r="F32" s="9"/>
       <x:c r="G32" s="9"/>
       <x:c r="H32" s="32"/>
+      <x:c r="I32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9"/>
@@ -3800,6 +4469,7 @@
       <x:c r="F33" s="9"/>
       <x:c r="G33" s="9"/>
       <x:c r="H33" s="32"/>
+      <x:c r="I33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="9"/>
@@ -3810,6 +4480,7 @@
       <x:c r="F34" s="9"/>
       <x:c r="G34" s="9"/>
       <x:c r="H34" s="32"/>
+      <x:c r="I34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9"/>
@@ -3820,6 +4491,7 @@
       <x:c r="F35" s="9"/>
       <x:c r="G35" s="9"/>
       <x:c r="H35" s="32"/>
+      <x:c r="I35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="9"/>
@@ -3830,6 +4502,7 @@
       <x:c r="F36" s="9"/>
       <x:c r="G36" s="9"/>
       <x:c r="H36" s="32"/>
+      <x:c r="I36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="9"/>
@@ -3840,6 +4513,7 @@
       <x:c r="F37" s="9"/>
       <x:c r="G37" s="9"/>
       <x:c r="H37" s="32"/>
+      <x:c r="I37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="9"/>
@@ -3850,6 +4524,7 @@
       <x:c r="F38" s="9"/>
       <x:c r="G38" s="9"/>
       <x:c r="H38" s="32"/>
+      <x:c r="I38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="9"/>
@@ -3860,6 +4535,7 @@
       <x:c r="F39" s="9"/>
       <x:c r="G39" s="9"/>
       <x:c r="H39" s="32"/>
+      <x:c r="I39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="9"/>
@@ -3870,6 +4546,7 @@
       <x:c r="F40" s="9"/>
       <x:c r="G40" s="9"/>
       <x:c r="H40" s="32"/>
+      <x:c r="I40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="9"/>
@@ -3880,6 +4557,7 @@
       <x:c r="F41" s="9"/>
       <x:c r="G41" s="9"/>
       <x:c r="H41" s="32"/>
+      <x:c r="I41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="9"/>
@@ -3890,6 +4568,7 @@
       <x:c r="F42" s="9"/>
       <x:c r="G42" s="9"/>
       <x:c r="H42" s="32"/>
+      <x:c r="I42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="9"/>
@@ -3900,6 +4579,7 @@
       <x:c r="F43" s="9"/>
       <x:c r="G43" s="9"/>
       <x:c r="H43" s="32"/>
+      <x:c r="I43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="9"/>
@@ -3910,6 +4590,7 @@
       <x:c r="F44" s="9"/>
       <x:c r="G44" s="9"/>
       <x:c r="H44" s="32"/>
+      <x:c r="I44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="9"/>
@@ -3920,6 +4601,7 @@
       <x:c r="F45" s="9"/>
       <x:c r="G45" s="9"/>
       <x:c r="H45" s="32"/>
+      <x:c r="I45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="9"/>
@@ -3930,6 +4612,7 @@
       <x:c r="F46" s="9"/>
       <x:c r="G46" s="9"/>
       <x:c r="H46" s="32"/>
+      <x:c r="I46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="9"/>
@@ -3940,6 +4623,7 @@
       <x:c r="F47" s="9"/>
       <x:c r="G47" s="9"/>
       <x:c r="H47" s="32"/>
+      <x:c r="I47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="9"/>
@@ -3950,6 +4634,7 @@
       <x:c r="F48" s="9"/>
       <x:c r="G48" s="9"/>
       <x:c r="H48" s="32"/>
+      <x:c r="I48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="9"/>
@@ -3960,6 +4645,7 @@
       <x:c r="F49" s="9"/>
       <x:c r="G49" s="9"/>
       <x:c r="H49" s="32"/>
+      <x:c r="I49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="9"/>
@@ -3970,6 +4656,7 @@
       <x:c r="F50" s="9"/>
       <x:c r="G50" s="9"/>
       <x:c r="H50" s="32"/>
+      <x:c r="I50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="9"/>
@@ -3980,6 +4667,7 @@
       <x:c r="F51" s="9"/>
       <x:c r="G51" s="9"/>
       <x:c r="H51" s="32"/>
+      <x:c r="I51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="9"/>
@@ -3990,6 +4678,7 @@
       <x:c r="F52" s="9"/>
       <x:c r="G52" s="9"/>
       <x:c r="H52" s="32"/>
+      <x:c r="I52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="9"/>
@@ -4000,6 +4689,7 @@
       <x:c r="F53" s="9"/>
       <x:c r="G53" s="9"/>
       <x:c r="H53" s="32"/>
+      <x:c r="I53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="9"/>
@@ -4010,6 +4700,7 @@
       <x:c r="F54" s="9"/>
       <x:c r="G54" s="9"/>
       <x:c r="H54" s="32"/>
+      <x:c r="I54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="9"/>
@@ -4020,6 +4711,7 @@
       <x:c r="F55" s="9"/>
       <x:c r="G55" s="9"/>
       <x:c r="H55" s="32"/>
+      <x:c r="I55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="9"/>
@@ -4030,6 +4722,7 @@
       <x:c r="F56" s="9"/>
       <x:c r="G56" s="9"/>
       <x:c r="H56" s="32"/>
+      <x:c r="I56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="9"/>
@@ -4040,6 +4733,7 @@
       <x:c r="F57" s="9"/>
       <x:c r="G57" s="9"/>
       <x:c r="H57" s="32"/>
+      <x:c r="I57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="9"/>
@@ -4050,6 +4744,7 @@
       <x:c r="F58" s="9"/>
       <x:c r="G58" s="9"/>
       <x:c r="H58" s="32"/>
+      <x:c r="I58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="9"/>
@@ -4060,6 +4755,7 @@
       <x:c r="F59" s="9"/>
       <x:c r="G59" s="9"/>
       <x:c r="H59" s="32"/>
+      <x:c r="I59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="9"/>
@@ -4070,6 +4766,7 @@
       <x:c r="F60" s="9"/>
       <x:c r="G60" s="9"/>
       <x:c r="H60" s="32"/>
+      <x:c r="I60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="9"/>
@@ -4080,6 +4777,7 @@
       <x:c r="F61" s="9"/>
       <x:c r="G61" s="9"/>
       <x:c r="H61" s="32"/>
+      <x:c r="I61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="9"/>
@@ -4090,6 +4788,7 @@
       <x:c r="F62" s="9"/>
       <x:c r="G62" s="9"/>
       <x:c r="H62" s="32"/>
+      <x:c r="I62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="9"/>
@@ -4100,6 +4799,7 @@
       <x:c r="F63" s="9"/>
       <x:c r="G63" s="9"/>
       <x:c r="H63" s="32"/>
+      <x:c r="I63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="9"/>
@@ -4110,6 +4810,7 @@
       <x:c r="F64" s="9"/>
       <x:c r="G64" s="9"/>
       <x:c r="H64" s="32"/>
+      <x:c r="I64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="9"/>
@@ -4120,6 +4821,7 @@
       <x:c r="F65" s="9"/>
       <x:c r="G65" s="9"/>
       <x:c r="H65" s="32"/>
+      <x:c r="I65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="9"/>
@@ -4130,6 +4832,7 @@
       <x:c r="F66" s="9"/>
       <x:c r="G66" s="9"/>
       <x:c r="H66" s="32"/>
+      <x:c r="I66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="9"/>
@@ -4140,6 +4843,7 @@
       <x:c r="F67" s="9"/>
       <x:c r="G67" s="9"/>
       <x:c r="H67" s="32"/>
+      <x:c r="I67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="9"/>
@@ -4150,6 +4854,7 @@
       <x:c r="F68" s="9"/>
       <x:c r="G68" s="9"/>
       <x:c r="H68" s="32"/>
+      <x:c r="I68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="9"/>
@@ -4160,6 +4865,7 @@
       <x:c r="F69" s="9"/>
       <x:c r="G69" s="9"/>
       <x:c r="H69" s="32"/>
+      <x:c r="I69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="9"/>
@@ -4170,6 +4876,7 @@
       <x:c r="F70" s="9"/>
       <x:c r="G70" s="9"/>
       <x:c r="H70" s="32"/>
+      <x:c r="I70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="9"/>
@@ -4180,6 +4887,7 @@
       <x:c r="F71" s="9"/>
       <x:c r="G71" s="9"/>
       <x:c r="H71" s="32"/>
+      <x:c r="I71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="9"/>
@@ -4190,6 +4898,7 @@
       <x:c r="F72" s="9"/>
       <x:c r="G72" s="9"/>
       <x:c r="H72" s="32"/>
+      <x:c r="I72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="9"/>
@@ -4200,6 +4909,7 @@
       <x:c r="F73" s="9"/>
       <x:c r="G73" s="9"/>
       <x:c r="H73" s="32"/>
+      <x:c r="I73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="9"/>
@@ -4210,6 +4920,7 @@
       <x:c r="F74" s="9"/>
       <x:c r="G74" s="9"/>
       <x:c r="H74" s="32"/>
+      <x:c r="I74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="9"/>
@@ -4220,6 +4931,7 @@
       <x:c r="F75" s="9"/>
       <x:c r="G75" s="9"/>
       <x:c r="H75" s="32"/>
+      <x:c r="I75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="9"/>
@@ -4230,6 +4942,7 @@
       <x:c r="F76" s="9"/>
       <x:c r="G76" s="9"/>
       <x:c r="H76" s="32"/>
+      <x:c r="I76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="9"/>
@@ -4240,6 +4953,7 @@
       <x:c r="F77" s="9"/>
       <x:c r="G77" s="9"/>
       <x:c r="H77" s="32"/>
+      <x:c r="I77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="9"/>
@@ -4250,6 +4964,7 @@
       <x:c r="F78" s="9"/>
       <x:c r="G78" s="9"/>
       <x:c r="H78" s="32"/>
+      <x:c r="I78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="9"/>
@@ -4260,6 +4975,7 @@
       <x:c r="F79" s="9"/>
       <x:c r="G79" s="9"/>
       <x:c r="H79" s="32"/>
+      <x:c r="I79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="9"/>
@@ -4270,6 +4986,7 @@
       <x:c r="F80" s="9"/>
       <x:c r="G80" s="9"/>
       <x:c r="H80" s="32"/>
+      <x:c r="I80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="9"/>
@@ -4280,6 +4997,7 @@
       <x:c r="F81" s="9"/>
       <x:c r="G81" s="9"/>
       <x:c r="H81" s="32"/>
+      <x:c r="I81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="9"/>
@@ -4290,6 +5008,7 @@
       <x:c r="F82" s="9"/>
       <x:c r="G82" s="9"/>
       <x:c r="H82" s="32"/>
+      <x:c r="I82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="9"/>
@@ -4300,6 +5019,7 @@
       <x:c r="F83" s="9"/>
       <x:c r="G83" s="9"/>
       <x:c r="H83" s="32"/>
+      <x:c r="I83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="9"/>
@@ -4310,6 +5030,7 @@
       <x:c r="F84" s="9"/>
       <x:c r="G84" s="9"/>
       <x:c r="H84" s="32"/>
+      <x:c r="I84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="9"/>
@@ -4320,6 +5041,7 @@
       <x:c r="F85" s="9"/>
       <x:c r="G85" s="9"/>
       <x:c r="H85" s="32"/>
+      <x:c r="I85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="9"/>
@@ -4330,6 +5052,7 @@
       <x:c r="F86" s="9"/>
       <x:c r="G86" s="9"/>
       <x:c r="H86" s="32"/>
+      <x:c r="I86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="9"/>
@@ -4340,6 +5063,7 @@
       <x:c r="F87" s="9"/>
       <x:c r="G87" s="9"/>
       <x:c r="H87" s="32"/>
+      <x:c r="I87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="9"/>
@@ -4350,6 +5074,7 @@
       <x:c r="F88" s="9"/>
       <x:c r="G88" s="9"/>
       <x:c r="H88" s="32"/>
+      <x:c r="I88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="9"/>
@@ -4360,6 +5085,7 @@
       <x:c r="F89" s="9"/>
       <x:c r="G89" s="9"/>
       <x:c r="H89" s="32"/>
+      <x:c r="I89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="9"/>
@@ -4370,6 +5096,7 @@
       <x:c r="F90" s="9"/>
       <x:c r="G90" s="9"/>
       <x:c r="H90" s="32"/>
+      <x:c r="I90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="9"/>
@@ -4380,6 +5107,7 @@
       <x:c r="F91" s="9"/>
       <x:c r="G91" s="9"/>
       <x:c r="H91" s="32"/>
+      <x:c r="I91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="9"/>
@@ -4390,6 +5118,7 @@
       <x:c r="F92" s="9"/>
       <x:c r="G92" s="9"/>
       <x:c r="H92" s="32"/>
+      <x:c r="I92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="9"/>
@@ -4400,6 +5129,7 @@
       <x:c r="F93" s="9"/>
       <x:c r="G93" s="9"/>
       <x:c r="H93" s="32"/>
+      <x:c r="I93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="9"/>
@@ -4410,6 +5140,7 @@
       <x:c r="F94" s="9"/>
       <x:c r="G94" s="9"/>
       <x:c r="H94" s="32"/>
+      <x:c r="I94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="9"/>
@@ -4420,6 +5151,7 @@
       <x:c r="F95" s="9"/>
       <x:c r="G95" s="9"/>
       <x:c r="H95" s="32"/>
+      <x:c r="I95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="9"/>
@@ -4430,6 +5162,7 @@
       <x:c r="F96" s="9"/>
       <x:c r="G96" s="9"/>
       <x:c r="H96" s="32"/>
+      <x:c r="I96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="9"/>
@@ -4440,6 +5173,7 @@
       <x:c r="F97" s="9"/>
       <x:c r="G97" s="9"/>
       <x:c r="H97" s="32"/>
+      <x:c r="I97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="9"/>
@@ -4450,6 +5184,7 @@
       <x:c r="F98" s="9"/>
       <x:c r="G98" s="9"/>
       <x:c r="H98" s="32"/>
+      <x:c r="I98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="9"/>
@@ -4460,6 +5195,7 @@
       <x:c r="F99" s="9"/>
       <x:c r="G99" s="9"/>
       <x:c r="H99" s="32"/>
+      <x:c r="I99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="9"/>
@@ -4470,6 +5206,7 @@
       <x:c r="F100" s="9"/>
       <x:c r="G100" s="9"/>
       <x:c r="H100" s="32"/>
+      <x:c r="I100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="9"/>
@@ -4480,6 +5217,7 @@
       <x:c r="F101" s="9"/>
       <x:c r="G101" s="9"/>
       <x:c r="H101" s="32"/>
+      <x:c r="I101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="9"/>
@@ -4490,6 +5228,7 @@
       <x:c r="F102" s="9"/>
       <x:c r="G102" s="9"/>
       <x:c r="H102" s="32"/>
+      <x:c r="I102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="9"/>
@@ -4500,6 +5239,7 @@
       <x:c r="F103" s="9"/>
       <x:c r="G103" s="9"/>
       <x:c r="H103" s="32"/>
+      <x:c r="I103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="9"/>
@@ -4510,6 +5250,7 @@
       <x:c r="F104" s="9"/>
       <x:c r="G104" s="9"/>
       <x:c r="H104" s="32"/>
+      <x:c r="I104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="9"/>
@@ -4520,6 +5261,7 @@
       <x:c r="F105" s="9"/>
       <x:c r="G105" s="9"/>
       <x:c r="H105" s="32"/>
+      <x:c r="I105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="9"/>
@@ -4530,6 +5272,7 @@
       <x:c r="F106" s="9"/>
       <x:c r="G106" s="9"/>
       <x:c r="H106" s="32"/>
+      <x:c r="I106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="9"/>
@@ -4540,6 +5283,7 @@
       <x:c r="F107" s="9"/>
       <x:c r="G107" s="9"/>
       <x:c r="H107" s="32"/>
+      <x:c r="I107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="9"/>
@@ -4550,6 +5294,7 @@
       <x:c r="F108" s="9"/>
       <x:c r="G108" s="9"/>
       <x:c r="H108" s="32"/>
+      <x:c r="I108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="9"/>
@@ -4560,6 +5305,7 @@
       <x:c r="F109" s="9"/>
       <x:c r="G109" s="9"/>
       <x:c r="H109" s="32"/>
+      <x:c r="I109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="9"/>
@@ -4570,6 +5316,7 @@
       <x:c r="F110" s="9"/>
       <x:c r="G110" s="9"/>
       <x:c r="H110" s="32"/>
+      <x:c r="I110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="9"/>
@@ -4580,6 +5327,7 @@
       <x:c r="F111" s="9"/>
       <x:c r="G111" s="9"/>
       <x:c r="H111" s="32"/>
+      <x:c r="I111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="9"/>
@@ -4590,6 +5338,7 @@
       <x:c r="F112" s="9"/>
       <x:c r="G112" s="9"/>
       <x:c r="H112" s="32"/>
+      <x:c r="I112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="9"/>
@@ -4600,6 +5349,7 @@
       <x:c r="F113" s="9"/>
       <x:c r="G113" s="9"/>
       <x:c r="H113" s="32"/>
+      <x:c r="I113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="9"/>
@@ -4610,6 +5360,7 @@
       <x:c r="F114" s="9"/>
       <x:c r="G114" s="9"/>
       <x:c r="H114" s="32"/>
+      <x:c r="I114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="9"/>
@@ -4620,6 +5371,7 @@
       <x:c r="F115" s="9"/>
       <x:c r="G115" s="9"/>
       <x:c r="H115" s="32"/>
+      <x:c r="I115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="9"/>
@@ -4630,6 +5382,7 @@
       <x:c r="F116" s="9"/>
       <x:c r="G116" s="9"/>
       <x:c r="H116" s="32"/>
+      <x:c r="I116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="9"/>
@@ -4640,6 +5393,7 @@
       <x:c r="F117" s="9"/>
       <x:c r="G117" s="9"/>
       <x:c r="H117" s="32"/>
+      <x:c r="I117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="9"/>
@@ -4650,6 +5404,7 @@
       <x:c r="F118" s="9"/>
       <x:c r="G118" s="9"/>
       <x:c r="H118" s="32"/>
+      <x:c r="I118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="9"/>
@@ -4660,6 +5415,7 @@
       <x:c r="F119" s="9"/>
       <x:c r="G119" s="9"/>
       <x:c r="H119" s="32"/>
+      <x:c r="I119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="9"/>
@@ -4670,6 +5426,7 @@
       <x:c r="F120" s="9"/>
       <x:c r="G120" s="9"/>
       <x:c r="H120" s="32"/>
+      <x:c r="I120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="9"/>
@@ -4680,6 +5437,7 @@
       <x:c r="F121" s="9"/>
       <x:c r="G121" s="9"/>
       <x:c r="H121" s="32"/>
+      <x:c r="I121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="9"/>
@@ -4690,6 +5448,7 @@
       <x:c r="F122" s="9"/>
       <x:c r="G122" s="9"/>
       <x:c r="H122" s="32"/>
+      <x:c r="I122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="9"/>
@@ -4700,6 +5459,7 @@
       <x:c r="F123" s="9"/>
       <x:c r="G123" s="9"/>
       <x:c r="H123" s="32"/>
+      <x:c r="I123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="9"/>
@@ -4710,11 +5470,252 @@
       <x:c r="F124" s="9"/>
       <x:c r="G124" s="9"/>
       <x:c r="H124" s="32"/>
+      <x:c r="I124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="I125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="I126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="I127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="I128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="I129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="I130"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="I131"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="I132"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="I133"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="I134"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="I135"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="I136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="I137"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="I138"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="I139"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="I140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="I141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="I142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="I143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="I144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="I145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="I146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="I147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="I148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="I149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="I150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="I151"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="I152"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="I153"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="I154"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="I155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="I156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="I157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="I158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="I159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="I160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="I161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="I162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="I163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="I164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="I165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="I166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="I167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="I168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="I169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="I170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="I171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="I172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="I173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="I174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="I175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="I176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="I177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="I178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="I179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="I180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="I181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="I182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="I183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="I184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="I185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="I186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="I187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="I188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="I189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="I190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="I191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="I192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="I193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="I194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="I195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="I196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="I197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="I198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="I199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="I200"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="I201"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="I202"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="I203"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="I204"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
   <x:dataValidations count="4">
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="Sole Type" error="Choose one of: EVA, PVC, PU, STUCK-ON" sqref="E10:E124">
@@ -4746,11 +5747,12 @@
     <x:col min="4" max="4" width="16" customWidth="1"/>
     <x:col min="5" max="5" width="28" customWidth="1"/>
     <x:col min="7" max="7" width="15" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -4760,8 +5762,8 @@
       <x:c r="G1" s="6"/>
     </x:row>
     <x:row r="2" ht="16" customHeight="1">
-      <x:c r="A2" s="7" t="s">
-        <x:v>52</x:v>
+      <x:c r="A2" s="7" t="str">
+        <x:v>Copy this pattern into BOM, Packing and Catalogue. Do not use this sheet as an upload tab.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -4772,77 +5774,680 @@
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="F4" s="8" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="G4" s="8" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="s">
-        <x:v>44</x:v>
+      <x:c r="H4" s="45" t="str">
+        <x:v>Size Run (optional)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="s">
+      <x:c r="F5" s="15" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F5" s="15" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="16">
         <x:v>0.42</x:v>
       </x:c>
+      <x:c r="H5" t="str">
+        <x:v>Small</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F6" s="15" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="G6" s="16">
         <x:v>1.2</x:v>
       </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="H28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="H29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="H30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="H37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="H38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="H39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="H40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="H41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="H42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="H43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="H44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="H45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="H46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="H47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="H48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="H49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="H50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="H51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="H52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="H53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="H54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="H55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="H56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="H57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="H58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="H59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="H60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="H61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="H62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="H63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="H64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="H65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="H66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="H67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="H68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="H69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="H70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="H71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="H72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="H73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="H74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="H75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="H76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="H77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="H78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="H79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="H80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="H81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="H82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="H83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="H84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="H85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="H86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="H87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="H88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="H89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="H90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="H91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="H92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="H93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="H94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="H95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="H96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="H97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="H98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="H99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="H100"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="H101"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="H102"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="H103"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="H104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="H105"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="H106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="H107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="H108"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="H109"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="H110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="H111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="H112"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="H113"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="H114"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="H115"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="H116"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="H117"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="H118"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="H119"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="H120"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="H121"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="H122"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="H123"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="H124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="H125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="H126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="H127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="H128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="H129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="H130"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="H131"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="H132"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="H133"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="H134"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="H135"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="H136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="H137"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="H138"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="H139"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="H140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="H141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="H142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="H143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="H144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="H145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="H146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="H147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="H148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="H149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="H150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="H151"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="H152"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="H153"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="H154"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="H155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="H156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="H157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="H158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="H159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="H160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="H161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="H162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="H163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="H164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="H165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="H166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="H167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="H168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="H169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="H170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="H171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="H172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="H173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="H174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="H175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="H176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="H177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="H178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="H179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="H180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="H181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="H182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="H183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="H184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="H185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="H186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="H187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="H188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="H189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="H190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="H191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="H192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="H193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="H194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="H195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="H196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="H197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="H198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="H199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="H200"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="H201"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="H202"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="H203"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="H204"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4865,7 +6470,7 @@
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -4874,7 +6479,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -4883,19 +6488,19 @@
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
         <x:v>Packing source</x:v>
@@ -4903,19 +6508,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D5" s="19">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E5" s="18" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F5" s="32" t="str">
         <x:v>SELF</x:v>
@@ -4923,19 +6528,19 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="20" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D6" s="22">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E6" s="21" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F6" s="32" t="str">
         <x:v>SELF</x:v>
@@ -4943,19 +6548,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D7" s="19">
         <x:v>112</x:v>
       </x:c>
       <x:c r="E7" s="18" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
         <x:v>SELF</x:v>
@@ -4963,19 +6568,19 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="20" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D8" s="22">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="21" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F8" s="32" t="str">
         <x:v>SELF</x:v>
@@ -4983,19 +6588,19 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="17" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D9" s="19">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="18" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>SELF</x:v>
@@ -5003,19 +6608,19 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="20" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D10" s="22">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="21" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>SELF</x:v>
@@ -5023,19 +6628,19 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B11" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D11" s="19">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="18" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>SELF</x:v>
@@ -5043,19 +6648,19 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="20" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D12" s="22">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="21" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>SELF</x:v>
@@ -5063,19 +6668,19 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B13" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D13" s="19">
         <x:v>144</x:v>
       </x:c>
       <x:c r="E13" s="18" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>ARMOUR</x:v>
@@ -5083,19 +6688,19 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="20" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="21" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="20" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D14" s="22">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E14" s="21" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>SELF</x:v>
@@ -5103,19 +6708,19 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B15" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D15" s="19">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E15" s="18" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>ARMOUR</x:v>
@@ -5123,19 +6728,19 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="20" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B16" s="21" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="20" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D16" s="22">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E16" s="21" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>ARMOUR</x:v>
@@ -5143,19 +6748,19 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B17" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D17" s="19">
         <x:v>140</x:v>
       </x:c>
       <x:c r="E17" s="18" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>ARMOUR</x:v>
@@ -5163,19 +6768,19 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="23" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B18" s="24" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C18" s="23" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D18" s="25" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E18" s="24" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>REX GOLA (V)</x:v>
@@ -5186,7 +6791,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B20" s="7"/>
       <x:c r="C20" s="7"/>
